--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -505,7 +505,7 @@
         <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
       </c>
       <c r="F9" t="str">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -520,10 +520,93 @@
       <c r="C11" t="str">
         <v>173_朱丽叶_Juliet_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F11" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>612_康乃馨古巴爱情_cuba love_undefined_20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>606_康乃馨橙光_orange_undefined_20stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>3</v>
+      </c>
+      <c r="C15" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="str">
+        <v>137_凯瑟琳_Catherine_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="str">
+        <v>610_康乃馨黄_yellow_undefined_20stems</v>
+      </c>
+      <c r="F20" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -578,7 +661,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.55854106590</v>
+        <v>08.55854106109815559811150</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -603,6 +603,9 @@
       <c r="A21" t="str">
         <v>4</v>
       </c>
+      <c r="C21" t="str">
+        <v>103_绣球莫奈粉_Hydrangea Vintage Blue_Hydrangea L._1stem</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -604,7 +604,7 @@
         <v>4</v>
       </c>
       <c r="C21" t="str">
-        <v>103_绣球莫奈粉_Hydrangea Vintage Blue_Hydrangea L._1stem</v>
+        <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -606,6 +606,9 @@
       <c r="C21" t="str">
         <v>154_莫泊_Moab_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F21" t="str">
+        <v>9</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -664,7 +667,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.55854106109815559811150</v>
+        <v>08.55854106109815559811159</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -610,9 +610,89 @@
         <v>9</v>
       </c>
     </row>
+    <row r="22">
+      <c r="C22" t="str">
+        <v>135_甜蜜曼塔_sweet menta_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>175_火灵鸟_Free Spirit_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>234_白泡泡_White Bubbles_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>5</v>
+      </c>
+      <c r="C28" t="str">
+        <v>3_波浪白洋桔梗_Wavy White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F28" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="str">
+        <v>12_肉粉洋桔梗_Peach Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F29" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>13_酒红洋桔梗_Burgundy Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F30" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="str">
+        <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -667,7 +747,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.55854106109815559811159</v>
+        <v>08.5585410610981555981115988551010151550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -689,6 +689,9 @@
       <c r="C31" t="str">
         <v>9_茶色洋桔梗_Tea Color Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
       </c>
+      <c r="F31" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -747,7 +750,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.5585410610981555981115988551010151550</v>
+        <v>08.5585410610981555981115988551010151555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -693,9 +693,89 @@
         <v>5</v>
       </c>
     </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>15_深紫洋桔梗_Dark Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F32" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>11_香槟洋桔梗_Champagne Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F33" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>14_波浪浅紫洋桔梗_Wavy Light Purple Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F34" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>384_奶油向日葵_sunflower cream_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="str">
+        <v>478_绿芯向日葵_sunflower mini_undefined_1bunch</v>
+      </c>
+      <c r="F36" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>6</v>
+      </c>
+      <c r="C37" t="str">
+        <v>1_白洋桔梗_White Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F37" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F38" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F39" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="str">
+        <v>623_多丁粉太子_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F40" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>626_多丁莫言_undefined_undefined_1bunch</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -750,7 +830,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.5585410610981555981115988551010151555</v>
+        <v>08.558541061098155598111598855101015155551010551055100</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -772,10 +772,90 @@
       <c r="C41" t="str">
         <v>626_多丁莫言_undefined_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>624_多丁白_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F42" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="str">
+        <v>614_康乃馨绿_green_undefined_20stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>615_康乃馨野马_horse_undefined_20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="str">
+        <v>621_康乃馨桃红_undefined_undefined_20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>611_康乃馨奶油白_cream white_undefined_20stems</v>
+      </c>
+      <c r="F46" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>631_吸色康乃馨宝蓝_tinted blue_undefined_20stems</v>
+      </c>
+      <c r="F47" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>630_吸色康乃馨天蓝_tinted tiffany blue_undefined_20stems</v>
+      </c>
+      <c r="F48" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>848_吸色康乃馨墨兰_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F49" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="str">
+        <v>632_吸色康乃馨紫_tinted purple_undefined_20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -830,7 +910,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.558541061098155598111598855101015155551010551055100</v>
+        <v>08.558541061098155598111598855101015155551010551055101055555105550</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -852,6 +852,9 @@
       <c r="C51" t="str">
         <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
       </c>
+      <c r="F51" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -910,7 +913,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.558541061098155598111598855101015155551010551055101055555105550</v>
+        <v>08.558541061098155598111598855101015155551010551055101055555105555</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
+++ b/DateBase/orders/Dang Nguyen48_2026-5-11.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -856,9 +856,44 @@
         <v>5</v>
       </c>
     </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>77_珍爱mini_undefined_Gerbera L._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>7</v>
+      </c>
+      <c r="C53" t="str">
+        <v>323_木绣球_Green snowball viburnum_undefined_1bunch</v>
+      </c>
+      <c r="F53" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>503_丁香花 粉_lilac pink_undefined_1bunch</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>447_黄金球_craspedia_undefined_1bunch</v>
+      </c>
+      <c r="F55" t="str">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L55"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -913,7 +948,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>08.558541061098155598111598855101015155551010551055101055555105555</v>
+        <v>08.55854106109815559811159885510101515555101055105510105555510555510101010</v>
       </c>
     </row>
   </sheetData>
